--- a/output/2026-09-15_20_Croazia_Brodsko-posavska_Cleaning.xlsx
+++ b/output/2026-09-15_20_Croazia_Brodsko-posavska_Cleaning.xlsx
@@ -495,7 +495,6 @@
           <t>035/495-509</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Rivenditore autorizzato Kärcher confermato (macchine lavaggio/pulizia, aspiratori professionali). Filiale verificata all'indirizzo J. J. Strossmayera 9 tramite listing ufficiali (centar-tehnike.hr/lokacije-trgovina, mojkatalog, katalog24). Sede legale gruppo a Osijek; email generica specifica per la filiale non reperita.</t>
@@ -503,7 +502,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -533,7 +532,6 @@
           <t>+385 35 640 111</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Filiale confermata (aperta settembre 2024) su hgspot.hr/poslovnice/slavonski-brod, indirizzo Tome Skalice 6. Categoria dedicata 'Industrijski usisavači' e pagina brand Kärcher aspiratori industriali. Email generica non reperita.</t>
@@ -541,7 +539,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
